--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:21</t>
+    <t xml:space="preserve">2026-09-10 01:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:35</t>
+    <t xml:space="preserve">2026-09-18 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:31</t>
+    <t xml:space="preserve">2026-09-23 15:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
-    <t xml:space="preserve">Juan Fernandez</t>
+    <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
     <t xml:space="preserve">Puchuncaví</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:35</t>
+    <t xml:space="preserve">2026-10-04 10:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:47</t>
+    <t xml:space="preserve">2026-10-05 16:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
